--- a/project/evaluations/VLM_Bert_Scores.xlsx
+++ b/project/evaluations/VLM_Bert_Scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G360"/>
+  <dimension ref="A1:F360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,11 +459,6 @@
           <t>VLM_F1_Score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>VLM_BLEU_Score</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -490,11 +485,6 @@
       <c r="F2" t="n">
         <v>0.8104079365730286</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -521,11 +511,6 @@
       <c r="F3" t="n">
         <v>0.8121342658996582</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,11 +537,6 @@
       <c r="F4" t="n">
         <v>0.8166962862014771</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,11 +563,6 @@
       <c r="F5" t="n">
         <v>0.8173877596855164</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -614,11 +589,6 @@
       <c r="F6" t="n">
         <v>0.8190221786499023</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -645,11 +615,6 @@
       <c r="F7" t="n">
         <v>0.8691824674606323</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -676,11 +641,6 @@
       <c r="F8" t="n">
         <v>0.8667469024658203</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -707,11 +667,6 @@
       <c r="F9" t="n">
         <v>0.8661404252052307</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,11 +693,6 @@
       <c r="F10" t="n">
         <v>0.8282363414764404</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -769,11 +719,6 @@
       <c r="F11" t="n">
         <v>0.8224130868911743</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -800,11 +745,6 @@
       <c r="F12" t="n">
         <v>0.8196747899055481</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -831,11 +771,6 @@
       <c r="F13" t="n">
         <v>0.812033474445343</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -862,11 +797,6 @@
       <c r="F14" t="n">
         <v>0.8602784872055054</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -893,11 +823,6 @@
       <c r="F15" t="n">
         <v>0.8156608939170837</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -924,11 +849,6 @@
       <c r="F16" t="n">
         <v>0.8153314590454102</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -955,11 +875,6 @@
       <c r="F17" t="n">
         <v>0.8636234402656555</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -986,11 +901,6 @@
       <c r="F18" t="n">
         <v>0.8290528655052185</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1017,11 +927,6 @@
       <c r="F19" t="n">
         <v>0.8388963341712952</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1048,11 +953,6 @@
       <c r="F20" t="n">
         <v>0.8336758613586426</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1079,11 +979,6 @@
       <c r="F21" t="n">
         <v>0.8344270586967468</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1110,11 +1005,6 @@
       <c r="F22" t="n">
         <v>0.8300855755805969</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1141,11 +1031,6 @@
       <c r="F23" t="n">
         <v>0.8533753156661987</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1172,11 +1057,6 @@
       <c r="F24" t="n">
         <v>0.8266756534576416</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1203,11 +1083,6 @@
       <c r="F25" t="n">
         <v>0.8582974672317505</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1234,11 +1109,6 @@
       <c r="F26" t="n">
         <v>0.8536736965179443</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1265,11 +1135,6 @@
       <c r="F27" t="n">
         <v>0.8212271332740784</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1296,11 +1161,6 @@
       <c r="F28" t="n">
         <v>0.8333548307418823</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1327,11 +1187,6 @@
       <c r="F29" t="n">
         <v>0.8315065503120422</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1358,11 +1213,6 @@
       <c r="F30" t="n">
         <v>0.8256924748420715</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1389,11 +1239,6 @@
       <c r="F31" t="n">
         <v>0.8362351059913635</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1420,11 +1265,6 @@
       <c r="F32" t="n">
         <v>0.8213984370231628</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1451,11 +1291,6 @@
       <c r="F33" t="n">
         <v>0.8162652850151062</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1482,11 +1317,6 @@
       <c r="F34" t="n">
         <v>0.8345763683319092</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1513,11 +1343,6 @@
       <c r="F35" t="n">
         <v>0.8352174162864685</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1544,11 +1369,6 @@
       <c r="F36" t="n">
         <v>0.8282884359359741</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1575,11 +1395,6 @@
       <c r="F37" t="n">
         <v>0.8271483182907104</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1606,11 +1421,6 @@
       <c r="F38" t="n">
         <v>0.8581749796867371</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1637,11 +1447,6 @@
       <c r="F39" t="n">
         <v>0.858512818813324</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1668,11 +1473,6 @@
       <c r="F40" t="n">
         <v>0.8627654314041138</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1699,11 +1499,6 @@
       <c r="F41" t="n">
         <v>0.8219241499900818</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1730,11 +1525,6 @@
       <c r="F42" t="n">
         <v>0.8351890444755554</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1761,11 +1551,6 @@
       <c r="F43" t="n">
         <v>0.8341311812400818</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1792,11 +1577,6 @@
       <c r="F44" t="n">
         <v>0.8371797800064087</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1823,11 +1603,6 @@
       <c r="F45" t="n">
         <v>0.831192672252655</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1854,11 +1629,6 @@
       <c r="F46" t="n">
         <v>0.8290758728981018</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1885,11 +1655,6 @@
       <c r="F47" t="n">
         <v>0.8318074345588684</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1916,11 +1681,6 @@
       <c r="F48" t="n">
         <v>0.8272373676300049</v>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1947,11 +1707,6 @@
       <c r="F49" t="n">
         <v>0.8291190266609192</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1978,11 +1733,6 @@
       <c r="F50" t="n">
         <v>0.8610891699790955</v>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2009,11 +1759,6 @@
       <c r="F51" t="n">
         <v>0.8673582077026367</v>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2040,11 +1785,6 @@
       <c r="F52" t="n">
         <v>0.8086445331573486</v>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2071,11 +1811,6 @@
       <c r="F53" t="n">
         <v>0.8288602232933044</v>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2102,11 +1837,6 @@
       <c r="F54" t="n">
         <v>0.8360096216201782</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2133,11 +1863,6 @@
       <c r="F55" t="n">
         <v>0.8606308698654175</v>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2164,11 +1889,6 @@
       <c r="F56" t="n">
         <v>0.8586904406547546</v>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2195,11 +1915,6 @@
       <c r="F57" t="n">
         <v>0.859056293964386</v>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2226,11 +1941,6 @@
       <c r="F58" t="n">
         <v>0.8520937561988831</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2257,11 +1967,6 @@
       <c r="F59" t="n">
         <v>0.8506330251693726</v>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2288,11 +1993,6 @@
       <c r="F60" t="n">
         <v>0.8546349406242371</v>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2319,11 +2019,6 @@
       <c r="F61" t="n">
         <v>0.8755031824111938</v>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2350,11 +2045,6 @@
       <c r="F62" t="n">
         <v>0.8583989143371582</v>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2381,11 +2071,6 @@
       <c r="F63" t="n">
         <v>0.8551519513130188</v>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2412,11 +2097,6 @@
       <c r="F64" t="n">
         <v>0.871116578578949</v>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2443,11 +2123,6 @@
       <c r="F65" t="n">
         <v>0.8661267757415771</v>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2474,11 +2149,6 @@
       <c r="F66" t="n">
         <v>0.8701000809669495</v>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2505,11 +2175,6 @@
       <c r="F67" t="n">
         <v>0.8723755478858948</v>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2536,11 +2201,6 @@
       <c r="F68" t="n">
         <v>0.8772590756416321</v>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2567,11 +2227,6 @@
       <c r="F69" t="n">
         <v>0.8821387887001038</v>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2598,11 +2253,6 @@
       <c r="F70" t="n">
         <v>0.8793882131576538</v>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2629,11 +2279,6 @@
       <c r="F71" t="n">
         <v>0.8868300318717957</v>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2660,11 +2305,6 @@
       <c r="F72" t="n">
         <v>0.8889941573143005</v>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2691,11 +2331,6 @@
       <c r="F73" t="n">
         <v>0.875633716583252</v>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2722,11 +2357,6 @@
       <c r="F74" t="n">
         <v>0.8771321177482605</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2753,11 +2383,6 @@
       <c r="F75" t="n">
         <v>0.8757553100585938</v>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2784,11 +2409,6 @@
       <c r="F76" t="n">
         <v>0.8573395013809204</v>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2815,11 +2435,6 @@
       <c r="F77" t="n">
         <v>0.8650490641593933</v>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2846,11 +2461,6 @@
       <c r="F78" t="n">
         <v>0.8622875213623047</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2877,11 +2487,6 @@
       <c r="F79" t="n">
         <v>0.856002151966095</v>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2908,11 +2513,6 @@
       <c r="F80" t="n">
         <v>0.8562625646591187</v>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2939,11 +2539,6 @@
       <c r="F81" t="n">
         <v>0.8642727136611938</v>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2970,11 +2565,6 @@
       <c r="F82" t="n">
         <v>0.8582701683044434</v>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3001,11 +2591,6 @@
       <c r="F83" t="n">
         <v>0.8675889372825623</v>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3032,11 +2617,6 @@
       <c r="F84" t="n">
         <v>0.8570808172225952</v>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3063,11 +2643,6 @@
       <c r="F85" t="n">
         <v>0.8654325008392334</v>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3094,11 +2669,6 @@
       <c r="F86" t="n">
         <v>0.86235511302948</v>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3125,11 +2695,6 @@
       <c r="F87" t="n">
         <v>0.8631309270858765</v>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3156,11 +2721,6 @@
       <c r="F88" t="n">
         <v>0.8614011406898499</v>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3187,11 +2747,6 @@
       <c r="F89" t="n">
         <v>0.8601003885269165</v>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3218,11 +2773,6 @@
       <c r="F90" t="n">
         <v>0.864013135433197</v>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3249,11 +2799,6 @@
       <c r="F91" t="n">
         <v>0.8537728190422058</v>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3280,11 +2825,6 @@
       <c r="F92" t="n">
         <v>0.8657382726669312</v>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3311,11 +2851,6 @@
       <c r="F93" t="n">
         <v>0.85860675573349</v>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3342,11 +2877,6 @@
       <c r="F94" t="n">
         <v>0.8666956424713135</v>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3373,11 +2903,6 @@
       <c r="F95" t="n">
         <v>0.8752031922340393</v>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3404,11 +2929,6 @@
       <c r="F96" t="n">
         <v>0.8776113986968994</v>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3435,11 +2955,6 @@
       <c r="F97" t="n">
         <v>0.871666431427002</v>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3466,11 +2981,6 @@
       <c r="F98" t="n">
         <v>0.8685208559036255</v>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3497,11 +3007,6 @@
       <c r="F99" t="n">
         <v>0.8564040064811707</v>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3528,11 +3033,6 @@
       <c r="F100" t="n">
         <v>0.8672870993614197</v>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3559,11 +3059,6 @@
       <c r="F101" t="n">
         <v>0.8646987080574036</v>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3590,11 +3085,6 @@
       <c r="F102" t="n">
         <v>0.8686721324920654</v>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3621,11 +3111,6 @@
       <c r="F103" t="n">
         <v>0.876452624797821</v>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3652,11 +3137,6 @@
       <c r="F104" t="n">
         <v>0.8556356430053711</v>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3683,11 +3163,6 @@
       <c r="F105" t="n">
         <v>0.8589134812355042</v>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>BLEU = 1.05 6.5/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3714,11 +3189,6 @@
       <c r="F106" t="n">
         <v>0.8393464684486389</v>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3745,11 +3215,6 @@
       <c r="F107" t="n">
         <v>0.8471583724021912</v>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3776,11 +3241,6 @@
       <c r="F108" t="n">
         <v>0.8563169240951538</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3807,11 +3267,6 @@
       <c r="F109" t="n">
         <v>0.8555116057395935</v>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3838,11 +3293,6 @@
       <c r="F110" t="n">
         <v>0.8615522980690002</v>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3869,11 +3319,6 @@
       <c r="F111" t="n">
         <v>0.8605430126190186</v>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3900,11 +3345,6 @@
       <c r="F112" t="n">
         <v>0.8686707019805908</v>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3931,11 +3371,6 @@
       <c r="F113" t="n">
         <v>0.8630865216255188</v>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3962,11 +3397,6 @@
       <c r="F114" t="n">
         <v>0.8695567846298218</v>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3993,11 +3423,6 @@
       <c r="F115" t="n">
         <v>0.8558776378631592</v>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4024,11 +3449,6 @@
       <c r="F116" t="n">
         <v>0.8615807890892029</v>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4055,11 +3475,6 @@
       <c r="F117" t="n">
         <v>0.8666304349899292</v>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4086,11 +3501,6 @@
       <c r="F118" t="n">
         <v>0.8556241989135742</v>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4117,11 +3527,6 @@
       <c r="F119" t="n">
         <v>0.8562791347503662</v>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4148,11 +3553,6 @@
       <c r="F120" t="n">
         <v>0.856701135635376</v>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4179,11 +3579,6 @@
       <c r="F121" t="n">
         <v>0.8604711890220642</v>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4210,11 +3605,6 @@
       <c r="F122" t="n">
         <v>0.8534413576126099</v>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4241,11 +3631,6 @@
       <c r="F123" t="n">
         <v>0.8536311388015747</v>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4272,11 +3657,6 @@
       <c r="F124" t="n">
         <v>0.8598732948303223</v>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4303,11 +3683,6 @@
       <c r="F125" t="n">
         <v>0.860602080821991</v>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4334,11 +3709,6 @@
       <c r="F126" t="n">
         <v>0.8593146204948425</v>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4365,11 +3735,6 @@
       <c r="F127" t="n">
         <v>0.8569528460502625</v>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4396,11 +3761,6 @@
       <c r="F128" t="n">
         <v>0.8554471135139465</v>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4427,11 +3787,6 @@
       <c r="F129" t="n">
         <v>0.865257203578949</v>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4458,11 +3813,6 @@
       <c r="F130" t="n">
         <v>0.8487629294395447</v>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4489,11 +3839,6 @@
       <c r="F131" t="n">
         <v>0.8546901345252991</v>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4520,11 +3865,6 @@
       <c r="F132" t="n">
         <v>0.8541654944419861</v>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4551,11 +3891,6 @@
       <c r="F133" t="n">
         <v>0.8589851856231689</v>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4582,11 +3917,6 @@
       <c r="F134" t="n">
         <v>0.8580066561698914</v>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4613,11 +3943,6 @@
       <c r="F135" t="n">
         <v>0.8584482669830322</v>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4644,11 +3969,6 @@
       <c r="F136" t="n">
         <v>0.8505024313926697</v>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4675,11 +3995,6 @@
       <c r="F137" t="n">
         <v>0.8518824577331543</v>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4706,11 +4021,6 @@
       <c r="F138" t="n">
         <v>0.856951892375946</v>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4737,11 +4047,6 @@
       <c r="F139" t="n">
         <v>0.8557018637657166</v>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4768,11 +4073,6 @@
       <c r="F140" t="n">
         <v>0.8508241176605225</v>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4799,11 +4099,6 @@
       <c r="F141" t="n">
         <v>0.8545750379562378</v>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4830,11 +4125,6 @@
       <c r="F142" t="n">
         <v>0.8490023016929626</v>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4861,11 +4151,6 @@
       <c r="F143" t="n">
         <v>0.8462868332862854</v>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4892,11 +4177,6 @@
       <c r="F144" t="n">
         <v>0.840267539024353</v>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4923,11 +4203,6 @@
       <c r="F145" t="n">
         <v>0.8478445410728455</v>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4954,11 +4229,6 @@
       <c r="F146" t="n">
         <v>0.8478256464004517</v>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4985,11 +4255,6 @@
       <c r="F147" t="n">
         <v>0.8387324810028076</v>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5016,11 +4281,6 @@
       <c r="F148" t="n">
         <v>0.8395727276802063</v>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5047,11 +4307,6 @@
       <c r="F149" t="n">
         <v>0.8399646282196045</v>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5078,11 +4333,6 @@
       <c r="F150" t="n">
         <v>0.8424620032310486</v>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5109,11 +4359,6 @@
       <c r="F151" t="n">
         <v>0.85346919298172</v>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5140,11 +4385,6 @@
       <c r="F152" t="n">
         <v>0.8544191122055054</v>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5171,11 +4411,6 @@
       <c r="F153" t="n">
         <v>0.8614243865013123</v>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5202,11 +4437,6 @@
       <c r="F154" t="n">
         <v>0.8514760732650757</v>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5233,11 +4463,6 @@
       <c r="F155" t="n">
         <v>0.8540524840354919</v>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5264,11 +4489,6 @@
       <c r="F156" t="n">
         <v>0.8513776063919067</v>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5295,11 +4515,6 @@
       <c r="F157" t="n">
         <v>0.8532310724258423</v>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5326,11 +4541,6 @@
       <c r="F158" t="n">
         <v>0.8551523685455322</v>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5357,11 +4567,6 @@
       <c r="F159" t="n">
         <v>0.8544467091560364</v>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5388,11 +4593,6 @@
       <c r="F160" t="n">
         <v>0.8539744019508362</v>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5419,11 +4619,6 @@
       <c r="F161" t="n">
         <v>0.8464201688766479</v>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5450,11 +4645,6 @@
       <c r="F162" t="n">
         <v>0.8497720956802368</v>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5481,11 +4671,6 @@
       <c r="F163" t="n">
         <v>0.845255434513092</v>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5512,11 +4697,6 @@
       <c r="F164" t="n">
         <v>0.8427582383155823</v>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5543,11 +4723,6 @@
       <c r="F165" t="n">
         <v>0.848493218421936</v>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5574,11 +4749,6 @@
       <c r="F166" t="n">
         <v>0.8408023715019226</v>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5605,11 +4775,6 @@
       <c r="F167" t="n">
         <v>0.843538761138916</v>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5636,11 +4801,6 @@
       <c r="F168" t="n">
         <v>0.8391811847686768</v>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5667,11 +4827,6 @@
       <c r="F169" t="n">
         <v>0.8407071232795715</v>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5698,11 +4853,6 @@
       <c r="F170" t="n">
         <v>0.847053587436676</v>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5729,11 +4879,6 @@
       <c r="F171" t="n">
         <v>0.8608188629150391</v>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5760,11 +4905,6 @@
       <c r="F172" t="n">
         <v>0.8720701336860657</v>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5791,11 +4931,6 @@
       <c r="F173" t="n">
         <v>0.8672807216644287</v>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5822,11 +4957,6 @@
       <c r="F174" t="n">
         <v>0.8695592284202576</v>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5853,11 +4983,6 @@
       <c r="F175" t="n">
         <v>0.8734458088874817</v>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5884,11 +5009,6 @@
       <c r="F176" t="n">
         <v>0.8597193360328674</v>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5915,11 +5035,6 @@
       <c r="F177" t="n">
         <v>0.8798334002494812</v>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5946,11 +5061,6 @@
       <c r="F178" t="n">
         <v>0.8731073141098022</v>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5977,11 +5087,6 @@
       <c r="F179" t="n">
         <v>0.8768453598022461</v>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6008,11 +5113,6 @@
       <c r="F180" t="n">
         <v>0.8715938925743103</v>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6039,11 +5139,6 @@
       <c r="F181" t="n">
         <v>0.8767223954200745</v>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6070,11 +5165,6 @@
       <c r="F182" t="n">
         <v>0.8743245601654053</v>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6101,11 +5191,6 @@
       <c r="F183" t="n">
         <v>0.8778708577156067</v>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6132,11 +5217,6 @@
       <c r="F184" t="n">
         <v>0.8775864243507385</v>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6163,11 +5243,6 @@
       <c r="F185" t="n">
         <v>0.8739737868309021</v>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6194,11 +5269,6 @@
       <c r="F186" t="n">
         <v>0.8701862096786499</v>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6225,11 +5295,6 @@
       <c r="F187" t="n">
         <v>0.8757603168487549</v>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6256,11 +5321,6 @@
       <c r="F188" t="n">
         <v>0.8744623064994812</v>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6287,11 +5347,6 @@
       <c r="F189" t="n">
         <v>0.8636394143104553</v>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6318,11 +5373,6 @@
       <c r="F190" t="n">
         <v>0.8685247302055359</v>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6349,11 +5399,6 @@
       <c r="F191" t="n">
         <v>0.8716672658920288</v>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6380,11 +5425,6 @@
       <c r="F192" t="n">
         <v>0.8673595190048218</v>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6411,11 +5451,6 @@
       <c r="F193" t="n">
         <v>0.8630412817001343</v>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6442,11 +5477,6 @@
       <c r="F194" t="n">
         <v>0.8663026094436646</v>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6473,11 +5503,6 @@
       <c r="F195" t="n">
         <v>0.8757613897323608</v>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6504,11 +5529,6 @@
       <c r="F196" t="n">
         <v>0.880528450012207</v>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6535,11 +5555,6 @@
       <c r="F197" t="n">
         <v>0.8699095249176025</v>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6566,11 +5581,6 @@
       <c r="F198" t="n">
         <v>0.863454282283783</v>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6597,11 +5607,6 @@
       <c r="F199" t="n">
         <v>0.8716792464256287</v>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6628,11 +5633,6 @@
       <c r="F200" t="n">
         <v>0.8720190525054932</v>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6659,11 +5659,6 @@
       <c r="F201" t="n">
         <v>0.8638991713523865</v>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6690,11 +5685,6 @@
       <c r="F202" t="n">
         <v>0.8744824528694153</v>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6721,11 +5711,6 @@
       <c r="F203" t="n">
         <v>0.8682118654251099</v>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6752,11 +5737,6 @@
       <c r="F204" t="n">
         <v>0.8651384711265564</v>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6783,11 +5763,6 @@
       <c r="F205" t="n">
         <v>0.8737258911132812</v>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6814,11 +5789,6 @@
       <c r="F206" t="n">
         <v>0.8649611473083496</v>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6845,11 +5815,6 @@
       <c r="F207" t="n">
         <v>0.8748679757118225</v>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6876,11 +5841,6 @@
       <c r="F208" t="n">
         <v>0.8766651153564453</v>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6907,11 +5867,6 @@
       <c r="F209" t="n">
         <v>0.8777207732200623</v>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6938,11 +5893,6 @@
       <c r="F210" t="n">
         <v>0.8695728778839111</v>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6969,11 +5919,6 @@
       <c r="F211" t="n">
         <v>0.869496762752533</v>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7000,11 +5945,6 @@
       <c r="F212" t="n">
         <v>0.8777661919593811</v>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7031,11 +5971,6 @@
       <c r="F213" t="n">
         <v>0.8710755705833435</v>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7062,11 +5997,6 @@
       <c r="F214" t="n">
         <v>0.8671963214874268</v>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7093,11 +6023,6 @@
       <c r="F215" t="n">
         <v>0.8694069981575012</v>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7124,11 +6049,6 @@
       <c r="F216" t="n">
         <v>0.8511501550674438</v>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7155,11 +6075,6 @@
       <c r="F217" t="n">
         <v>0.85451340675354</v>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7186,11 +6101,6 @@
       <c r="F218" t="n">
         <v>0.8519296646118164</v>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7217,11 +6127,6 @@
       <c r="F219" t="n">
         <v>0.8417444229125977</v>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7248,11 +6153,6 @@
       <c r="F220" t="n">
         <v>0.853388786315918</v>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7279,11 +6179,6 @@
       <c r="F221" t="n">
         <v>0.8651109337806702</v>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7310,11 +6205,6 @@
       <c r="F222" t="n">
         <v>0.8531536459922791</v>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7341,11 +6231,6 @@
       <c r="F223" t="n">
         <v>0.8474364280700684</v>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7372,11 +6257,6 @@
       <c r="F224" t="n">
         <v>0.8485319018363953</v>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7403,11 +6283,6 @@
       <c r="F225" t="n">
         <v>0.8582377433776855</v>
       </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7434,11 +6309,6 @@
       <c r="F226" t="n">
         <v>0.8468031883239746</v>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7465,11 +6335,6 @@
       <c r="F227" t="n">
         <v>0.8632494211196899</v>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7496,11 +6361,6 @@
       <c r="F228" t="n">
         <v>0.8715704679489136</v>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7527,11 +6387,6 @@
       <c r="F229" t="n">
         <v>0.8720541000366211</v>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7558,11 +6413,6 @@
       <c r="F230" t="n">
         <v>0.8602636456489563</v>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7589,11 +6439,6 @@
       <c r="F231" t="n">
         <v>0.8623840808868408</v>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7620,11 +6465,6 @@
       <c r="F232" t="n">
         <v>0.8582121133804321</v>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7651,11 +6491,6 @@
       <c r="F233" t="n">
         <v>0.8675474524497986</v>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7682,11 +6517,6 @@
       <c r="F234" t="n">
         <v>0.8541128635406494</v>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7713,11 +6543,6 @@
       <c r="F235" t="n">
         <v>0.8780012726783752</v>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7744,11 +6569,6 @@
       <c r="F236" t="n">
         <v>0.87645024061203</v>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7775,11 +6595,6 @@
       <c r="F237" t="n">
         <v>0.8719468116760254</v>
       </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7806,11 +6621,6 @@
       <c r="F238" t="n">
         <v>0.8825535774230957</v>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7837,11 +6647,6 @@
       <c r="F239" t="n">
         <v>0.8851045370101929</v>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7868,11 +6673,6 @@
       <c r="F240" t="n">
         <v>0.8826210498809814</v>
       </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>BLEU = 1.01 4.7/1.2/0.6/0.3 (BP = 1.000 ratio = 43.000 hyp_len = 43 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7899,11 +6699,6 @@
       <c r="F241" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7930,11 +6725,6 @@
       <c r="F242" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7961,11 +6751,6 @@
       <c r="F243" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7992,11 +6777,6 @@
       <c r="F244" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8023,11 +6803,6 @@
       <c r="F245" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8054,11 +6829,6 @@
       <c r="F246" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8085,11 +6855,6 @@
       <c r="F247" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8116,11 +6881,6 @@
       <c r="F248" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8147,11 +6907,6 @@
       <c r="F249" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8178,11 +6933,6 @@
       <c r="F250" t="n">
         <v>0.8813638091087341</v>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8209,11 +6959,6 @@
       <c r="F251" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8240,11 +6985,6 @@
       <c r="F252" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8271,11 +7011,6 @@
       <c r="F253" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8302,11 +7037,6 @@
       <c r="F254" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8333,11 +7063,6 @@
       <c r="F255" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8364,11 +7089,6 @@
       <c r="F256" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8395,11 +7115,6 @@
       <c r="F257" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8426,11 +7141,6 @@
       <c r="F258" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8457,11 +7167,6 @@
       <c r="F259" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8488,11 +7193,6 @@
       <c r="F260" t="n">
         <v>0.8904313445091248</v>
       </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8519,11 +7219,6 @@
       <c r="F261" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8550,11 +7245,6 @@
       <c r="F262" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8581,11 +7271,6 @@
       <c r="F263" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8612,11 +7297,6 @@
       <c r="F264" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8643,11 +7323,6 @@
       <c r="F265" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8674,11 +7349,6 @@
       <c r="F266" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8705,11 +7375,6 @@
       <c r="F267" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8736,11 +7401,6 @@
       <c r="F268" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8767,11 +7427,6 @@
       <c r="F269" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8798,11 +7453,6 @@
       <c r="F270" t="n">
         <v>0.8567204475402832</v>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8829,11 +7479,6 @@
       <c r="F271" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8860,11 +7505,6 @@
       <c r="F272" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8891,11 +7531,6 @@
       <c r="F273" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8922,11 +7557,6 @@
       <c r="F274" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8953,11 +7583,6 @@
       <c r="F275" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8984,11 +7609,6 @@
       <c r="F276" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9015,11 +7635,6 @@
       <c r="F277" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9046,11 +7661,6 @@
       <c r="F278" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9077,11 +7687,6 @@
       <c r="F279" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9108,11 +7713,6 @@
       <c r="F280" t="n">
         <v>0.8850266933441162</v>
       </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9139,11 +7739,6 @@
       <c r="F281" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9170,11 +7765,6 @@
       <c r="F282" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9201,11 +7791,6 @@
       <c r="F283" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9232,11 +7817,6 @@
       <c r="F284" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9263,11 +7843,6 @@
       <c r="F285" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9294,11 +7869,6 @@
       <c r="F286" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9325,11 +7895,6 @@
       <c r="F287" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9356,11 +7921,6 @@
       <c r="F288" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9387,11 +7947,6 @@
       <c r="F289" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9418,11 +7973,6 @@
       <c r="F290" t="n">
         <v>0.8770772814750671</v>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9449,11 +7999,6 @@
       <c r="F291" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9480,11 +8025,6 @@
       <c r="F292" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9511,11 +8051,6 @@
       <c r="F293" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9542,11 +8077,6 @@
       <c r="F294" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9573,11 +8103,6 @@
       <c r="F295" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9604,11 +8129,6 @@
       <c r="F296" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9635,11 +8155,6 @@
       <c r="F297" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9666,11 +8181,6 @@
       <c r="F298" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9697,11 +8207,6 @@
       <c r="F299" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -9728,11 +8233,6 @@
       <c r="F300" t="n">
         <v>0.8877978920936584</v>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -9759,11 +8259,6 @@
       <c r="F301" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -9790,11 +8285,6 @@
       <c r="F302" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -9821,11 +8311,6 @@
       <c r="F303" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -9852,11 +8337,6 @@
       <c r="F304" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -9883,11 +8363,6 @@
       <c r="F305" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -9914,11 +8389,6 @@
       <c r="F306" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -9945,11 +8415,6 @@
       <c r="F307" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -9976,11 +8441,6 @@
       <c r="F308" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10007,11 +8467,6 @@
       <c r="F309" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10038,11 +8493,6 @@
       <c r="F310" t="n">
         <v>0.8954070210456848</v>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10069,11 +8519,6 @@
       <c r="F311" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10100,11 +8545,6 @@
       <c r="F312" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10131,11 +8571,6 @@
       <c r="F313" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10162,11 +8597,6 @@
       <c r="F314" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10193,11 +8623,6 @@
       <c r="F315" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10224,11 +8649,6 @@
       <c r="F316" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10255,11 +8675,6 @@
       <c r="F317" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10286,11 +8701,6 @@
       <c r="F318" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10317,11 +8727,6 @@
       <c r="F319" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10348,11 +8753,6 @@
       <c r="F320" t="n">
         <v>0.8601572513580322</v>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>BLEU = 0.92 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 47.000 hyp_len = 47 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10379,11 +8779,6 @@
       <c r="F321" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10410,11 +8805,6 @@
       <c r="F322" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10441,11 +8831,6 @@
       <c r="F323" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10472,11 +8857,6 @@
       <c r="F324" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -10503,11 +8883,6 @@
       <c r="F325" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10534,11 +8909,6 @@
       <c r="F326" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10565,11 +8935,6 @@
       <c r="F327" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10596,11 +8961,6 @@
       <c r="F328" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10627,11 +8987,6 @@
       <c r="F329" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10658,11 +9013,6 @@
       <c r="F330" t="n">
         <v>0.8752602338790894</v>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>BLEU = 0.97 4.4/1.1/0.6/0.3 (BP = 1.000 ratio = 45.000 hyp_len = 45 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10689,11 +9039,6 @@
       <c r="F331" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -10720,11 +9065,6 @@
       <c r="F332" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -10751,11 +9091,6 @@
       <c r="F333" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -10782,11 +9117,6 @@
       <c r="F334" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -10813,11 +9143,6 @@
       <c r="F335" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -10844,11 +9169,6 @@
       <c r="F336" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -10875,11 +9195,6 @@
       <c r="F337" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -10906,11 +9221,6 @@
       <c r="F338" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -10937,11 +9247,6 @@
       <c r="F339" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -10968,11 +9273,6 @@
       <c r="F340" t="n">
         <v>0.8645458817481995</v>
       </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>BLEU = 0.99 4.5/1.2/0.6/0.3 (BP = 1.000 ratio = 44.000 hyp_len = 44 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -10999,11 +9299,6 @@
       <c r="F341" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11030,11 +9325,6 @@
       <c r="F342" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11061,11 +9351,6 @@
       <c r="F343" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11092,11 +9377,6 @@
       <c r="F344" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11123,11 +9403,6 @@
       <c r="F345" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11154,11 +9429,6 @@
       <c r="F346" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11185,11 +9455,6 @@
       <c r="F347" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -11216,11 +9481,6 @@
       <c r="F348" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11247,11 +9507,6 @@
       <c r="F349" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11278,11 +9533,6 @@
       <c r="F350" t="n">
         <v>0.8769310116767883</v>
       </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>BLEU = 0.95 4.3/1.1/0.6/0.3 (BP = 1.000 ratio = 46.000 hyp_len = 46 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -11309,11 +9559,6 @@
       <c r="F351" t="n">
         <v>0.8906723260879517</v>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -11340,11 +9585,6 @@
       <c r="F352" t="n">
         <v>0.8906723260879517</v>
       </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11371,11 +9611,6 @@
       <c r="F353" t="n">
         <v>0.8906723260879517</v>
       </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11402,11 +9637,6 @@
       <c r="F354" t="n">
         <v>0.8906723260879517</v>
       </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -11433,11 +9663,6 @@
       <c r="F355" t="n">
         <v>0.8906723260879517</v>
       </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11464,11 +9689,6 @@
       <c r="F356" t="n">
         <v>0.8906723260879517</v>
       </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11495,11 +9715,6 @@
       <c r="F357" t="n">
         <v>0.8906723260879517</v>
       </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -11526,11 +9741,6 @@
       <c r="F358" t="n">
         <v>0.8906723260879517</v>
       </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11557,11 +9767,6 @@
       <c r="F359" t="n">
         <v>0.8906723260879517</v>
       </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -11587,11 +9792,6 @@
       </c>
       <c r="F360" t="n">
         <v>0.8906723260879517</v>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>BLEU = 0.90 4.2/1.1/0.5/0.3 (BP = 1.000 ratio = 48.000 hyp_len = 48 ref_len = 1)</t>
-        </is>
       </c>
     </row>
   </sheetData>
